--- a/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
+++ b/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
+++ b/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
+++ b/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -478,7 +478,7 @@
     <t>Links EVS summary to specific mission</t>
   </si>
   <si>
-    <t>Links radiation exposure to specific space missions</t>
+    <t>Links clinical observations and events to specific space missions</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
+++ b/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
+++ b/docs/StructureDefinition-space-evs-minutes-per-week.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$73</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2836" uniqueCount="583">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/space-evs-minutes-per-week</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/space-evs-minutes-per-week</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -471,7 +474,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -491,7 +494,7 @@
     <t>derivedFromGroup</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/derived-from-group}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/derived-from-group}
 </t>
   </si>
   <si>
@@ -824,6 +827,151 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
+    <t>Observation.code.coding:loinc.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.system</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
     <t>Observation.code.text</t>
   </si>
   <si>
@@ -851,7 +999,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -1181,7 +1329,7 @@
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/evs-units-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/evs-units-vs</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -1955,54 +2103,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2012,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP66"/>
+  <dimension ref="A1:AP73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.03125" customWidth="true" bestFit="true"/>
@@ -2040,7 +2190,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="53.24609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.51953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.53515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -2060,149 +2210,149 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2214,16 +2364,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2273,31 +2423,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -2308,10 +2458,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2319,10 +2469,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2331,19 +2481,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2393,13 +2543,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2428,10 +2578,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2439,10 +2589,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2451,16 +2601,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2511,19 +2661,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2546,10 +2696,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2557,31 +2707,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2631,19 +2781,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2666,10 +2816,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2677,10 +2827,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2692,16 +2842,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2727,13 +2877,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2751,19 +2901,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2786,21 +2936,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2812,16 +2962,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2871,19 +3021,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2895,7 +3045,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -2906,21 +3056,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2932,16 +3082,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2991,13 +3141,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -3015,7 +3165,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -3026,10 +3176,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3037,10 +3187,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -3052,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3097,29 +3247,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3142,26 +3292,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -3170,13 +3320,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3227,19 +3377,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3262,26 +3412,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -3290,13 +3440,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3347,19 +3497,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3382,45 +3532,45 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3469,19 +3619,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -3493,7 +3643,7 @@
         <v>20</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>20</v>
@@ -3504,10 +3654,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3515,10 +3665,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3527,20 +3677,20 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3589,34 +3739,34 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>20</v>
@@ -3624,21 +3774,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3647,20 +3797,20 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3709,31 +3859,31 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>20</v>
@@ -3744,21 +3894,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3767,19 +3917,19 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3829,31 +3979,31 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>20</v>
@@ -3864,10 +4014,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3875,34 +4025,34 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3927,13 +4077,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3951,34 +4101,34 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -3986,10 +4136,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3997,13 +4147,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
@@ -4012,19 +4162,19 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -4049,41 +4199,41 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -4095,10 +4245,10 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>20</v>
@@ -4106,26 +4256,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -4134,19 +4284,19 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4156,7 +4306,7 @@
         <v>20</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>20</v>
@@ -4171,13 +4321,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4195,19 +4345,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -4219,10 +4369,10 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>20</v>
@@ -4230,45 +4380,45 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4293,13 +4443,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -4317,45 +4467,45 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4363,10 +4513,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4378,13 +4528,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4435,13 +4585,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -4459,7 +4609,7 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -4470,21 +4620,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4496,16 +4646,16 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4543,31 +4693,31 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
@@ -4579,7 +4729,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4590,10 +4740,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4601,10 +4751,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4613,22 +4763,22 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4665,29 +4815,29 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -4696,10 +4846,10 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -4710,47 +4860,47 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4760,7 +4910,7 @@
         <v>20</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>20</v>
@@ -4799,19 +4949,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4820,10 +4970,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -4834,10 +4984,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4845,10 +4995,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4857,23 +5007,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4921,19 +5067,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4942,10 +5088,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -4954,48 +5100,46 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>264</v>
+        <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -5031,46 +5175,46 @@
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -5078,10 +5222,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5089,10 +5233,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5101,21 +5245,23 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>274</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -5124,7 +5270,7 @@
         <v>20</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>20</v>
@@ -5163,19 +5309,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -5184,13 +5330,13 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>20</v>
@@ -5198,21 +5344,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -5221,23 +5367,21 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5285,80 +5429,78 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>292</v>
+        <v>113</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5407,34 +5549,34 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>20</v>
@@ -5442,10 +5584,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5453,10 +5595,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5465,21 +5607,21 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5527,19 +5669,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5548,13 +5690,13 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>20</v>
@@ -5562,10 +5704,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5573,10 +5715,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5585,20 +5727,22 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5647,45 +5791,45 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>317</v>
+        <v>20</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5693,34 +5837,34 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>233</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5769,45 +5913,45 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5815,31 +5959,35 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>232</v>
+        <v>313</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>233</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5887,34 +6035,34 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>235</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>20</v>
+        <v>319</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>20</v>
+        <v>321</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>20</v>
@@ -5922,21 +6070,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5945,19 +6093,19 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>323</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>238</v>
+        <v>324</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>239</v>
+        <v>325</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>159</v>
+        <v>326</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5995,31 +6143,31 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>241</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -6028,13 +6176,13 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>236</v>
+        <v>327</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>20</v>
+        <v>321</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>20</v>
@@ -6042,21 +6190,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6065,22 +6213,22 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6129,156 +6277,156 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AO34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="J35" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="P35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q35" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="R35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="Z35" t="s" s="2">
+      <c r="AI35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK35" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AA35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF35" t="s" s="2">
+      <c r="AL35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>20</v>
@@ -6297,10 +6445,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6309,21 +6457,21 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>232</v>
+        <v>351</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
         <v>353</v>
       </c>
+      <c r="N36" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6371,19 +6519,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6398,7 +6546,7 @@
         <v>356</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>20</v>
@@ -6406,10 +6554,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6417,10 +6565,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6429,20 +6577,20 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>106</v>
+        <v>359</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6452,7 +6600,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -6491,45 +6639,45 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>20</v>
+        <v>366</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6537,34 +6685,34 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>112</v>
+        <v>368</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6589,11 +6737,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6611,45 +6761,45 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>20</v>
+        <v>373</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>20</v>
+        <v>377</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6657,10 +6807,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6672,20 +6822,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>374</v>
+        <v>234</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6709,13 +6855,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6733,19 +6879,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>373</v>
+        <v>236</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6754,10 +6900,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>382</v>
+        <v>237</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6768,21 +6914,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>384</v>
+        <v>157</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6794,20 +6940,18 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>385</v>
+        <v>239</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>386</v>
+        <v>240</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6831,69 +6975,69 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>389</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>383</v>
+        <v>242</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>393</v>
+        <v>237</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6901,10 +7045,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6913,22 +7057,22 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6977,19 +7121,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6998,10 +7142,10 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7012,10 +7156,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7023,37 +7167,39 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q42" s="2"/>
+      <c r="Q42" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="R42" t="s" s="2">
         <v>20</v>
       </c>
@@ -7073,13 +7219,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -7097,45 +7243,45 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>409</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>412</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7143,10 +7289,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7155,22 +7301,20 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7195,13 +7339,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -7219,19 +7363,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7240,10 +7384,10 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7254,10 +7398,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7265,10 +7409,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7277,21 +7421,21 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7300,7 +7444,7 @@
         <v>20</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>20</v>
+        <v>410</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>20</v>
@@ -7339,45 +7483,45 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>20</v>
+        <v>412</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7385,10 +7529,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7397,21 +7541,23 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>432</v>
+        <v>113</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7435,13 +7581,11 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>20</v>
+        <v>419</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -7459,45 +7603,45 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>436</v>
+        <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>437</v>
+        <v>404</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>439</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7505,10 +7649,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7520,19 +7664,19 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>441</v>
+        <v>204</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7557,13 +7701,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>20</v>
+        <v>427</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>20</v>
+        <v>428</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7581,19 +7725,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>20</v>
+        <v>430</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>446</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7602,10 +7746,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>447</v>
+        <v>136</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7616,21 +7760,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7642,16 +7786,20 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>233</v>
+        <v>434</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7675,13 +7823,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>20</v>
+        <v>427</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>20</v>
+        <v>438</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>20</v>
+        <v>439</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7699,56 +7847,56 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>235</v>
+        <v>432</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>20</v>
+        <v>440</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>236</v>
+        <v>442</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>20</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7760,18 +7908,20 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>137</v>
+        <v>445</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>238</v>
+        <v>446</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>239</v>
+        <v>447</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7819,19 +7969,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>241</v>
+        <v>444</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7840,10 +7990,10 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>20</v>
+        <v>450</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>236</v>
+        <v>451</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7854,33 +8004,33 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>452</v>
+        <v>20</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>453</v>
@@ -7889,11 +8039,9 @@
         <v>454</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7917,13 +8065,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>20</v>
+        <v>457</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7941,45 +8089,45 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>20</v>
+        <v>459</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>135</v>
+        <v>460</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>20</v>
+        <v>461</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7987,10 +8135,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -8002,16 +8150,20 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>457</v>
+        <v>204</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -8035,13 +8187,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>20</v>
+        <v>467</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>20</v>
+        <v>468</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -8059,19 +8211,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>460</v>
+        <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8080,10 +8232,10 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8094,10 +8246,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8105,10 +8257,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8120,15 +8272,17 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8177,45 +8331,45 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>460</v>
+        <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>20</v>
+        <v>476</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>20</v>
+        <v>479</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8223,10 +8377,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8238,20 +8392,18 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>203</v>
+        <v>481</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -8275,13 +8427,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>472</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>473</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8299,45 +8451,45 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>393</v>
+        <v>487</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>20</v>
+        <v>488</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8345,10 +8497,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8360,19 +8512,19 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>203</v>
+        <v>490</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8397,13 +8549,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>481</v>
+        <v>20</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>482</v>
+        <v>20</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8421,31 +8573,31 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>495</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>474</v>
+        <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>393</v>
+        <v>497</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8456,10 +8608,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8467,10 +8619,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8482,18 +8634,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>484</v>
+        <v>233</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>485</v>
+        <v>234</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>486</v>
+        <v>235</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>487</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -8541,19 +8691,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>483</v>
+        <v>236</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8565,7 +8715,7 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>488</v>
+        <v>237</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8576,21 +8726,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8602,15 +8752,17 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>490</v>
+        <v>239</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8659,19 +8811,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>489</v>
+        <v>242</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8680,10 +8832,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>461</v>
+        <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>492</v>
+        <v>237</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8694,44 +8846,46 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>20</v>
+        <v>501</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>494</v>
+        <v>138</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -8779,19 +8933,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8800,10 +8954,10 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>498</v>
+        <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>499</v>
+        <v>136</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8814,10 +8968,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8825,10 +8979,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8837,20 +8991,18 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8899,19 +9051,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>20</v>
+        <v>509</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8920,10 +9072,10 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -8934,10 +9086,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8945,10 +9097,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8957,23 +9109,19 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>441</v>
+        <v>506</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -9021,19 +9169,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>20</v>
+        <v>509</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -9042,10 +9190,10 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9056,10 +9204,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9067,10 +9215,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9082,16 +9230,20 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>233</v>
+        <v>517</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
       </c>
@@ -9115,13 +9267,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>20</v>
+        <v>521</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>20</v>
+        <v>522</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9139,31 +9291,31 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>235</v>
+        <v>516</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>20</v>
+        <v>523</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>20</v>
+        <v>524</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>236</v>
+        <v>442</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9174,21 +9326,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9200,18 +9352,20 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>238</v>
+        <v>526</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>239</v>
+        <v>527</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -9235,13 +9389,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>20</v>
+        <v>530</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>20</v>
+        <v>531</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9259,31 +9413,31 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>241</v>
+        <v>525</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>20</v>
+        <v>523</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>20</v>
+        <v>524</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>236</v>
+        <v>442</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9294,45 +9448,43 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>452</v>
+        <v>20</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>137</v>
+        <v>533</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>453</v>
+        <v>534</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>160</v>
+        <v>536</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9381,19 +9533,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>455</v>
+        <v>532</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -9405,7 +9557,7 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>135</v>
+        <v>537</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9416,10 +9568,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9427,10 +9579,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9439,23 +9591,19 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>517</v>
+        <v>539</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
@@ -9479,13 +9627,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -9503,34 +9651,34 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>520</v>
+        <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>227</v>
+        <v>510</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>228</v>
+        <v>541</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>20</v>
@@ -9538,10 +9686,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9549,10 +9697,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9561,23 +9709,21 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>321</v>
+        <v>545</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
@@ -9625,45 +9771,45 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>525</v>
+        <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>326</v>
+        <v>547</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>327</v>
+        <v>548</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9671,10 +9817,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9683,23 +9829,21 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>203</v>
+        <v>550</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
@@ -9723,13 +9867,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9747,19 +9891,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9768,10 +9912,10 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>135</v>
+        <v>547</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>382</v>
+        <v>554</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -9782,21 +9926,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9805,22 +9949,22 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>203</v>
+        <v>490</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>385</v>
+        <v>556</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>386</v>
+        <v>557</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>387</v>
+        <v>558</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>388</v>
+        <v>559</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9845,13 +9989,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>389</v>
+        <v>20</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9869,45 +10013,45 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>392</v>
+        <v>560</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>393</v>
+        <v>561</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9915,10 +10059,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9930,20 +10074,16 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>532</v>
+        <v>234</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
       </c>
@@ -9991,19 +10131,19 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>531</v>
+        <v>236</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -10012,20 +10152,872 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>447</v>
+        <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>448</v>
+        <v>237</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP66" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP66">
+  <autoFilter ref="A1:AP73">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10035,7 +11027,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI72">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
